--- a/data-raw/clim1/keys/treatment-key-v1.xlsx
+++ b/data-raw/clim1/keys/treatment-key-v1.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4545F698-1605-4BA8-ACD8-9AD7B08FFE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41259E8-C9E8-4C40-9B6B-0F588011297F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="71">
   <si>
     <t>trial_location</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>26fall_APROW_wide_3QN</t>
+  </si>
+  <si>
+    <t>Note I had to change the trt_nus for some merging issues</t>
   </si>
 </sst>
 </file>
@@ -703,6 +706,11 @@
         <v>42</v>
       </c>
     </row>
+    <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
     <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>0</v>
@@ -745,9 +753,7 @@
       <c r="B7" s="4">
         <v>2026</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
@@ -775,9 +781,7 @@
     <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="4">
-        <v>2</v>
-      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
@@ -805,9 +809,7 @@
     <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="4">
-        <v>3</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
@@ -833,9 +835,7 @@
     <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="4">
-        <v>4</v>
-      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
@@ -861,9 +861,7 @@
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="4">
-        <v>5</v>
-      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
@@ -891,9 +889,7 @@
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="4">
-        <v>6</v>
-      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
@@ -919,9 +915,7 @@
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="4">
-        <v>7</v>
-      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="4" t="s">
         <v>69</v>
       </c>
@@ -949,9 +943,7 @@
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="4">
-        <v>8</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
         <v>21</v>
       </c>
@@ -977,9 +969,7 @@
     <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="4">
-        <v>9</v>
-      </c>
+      <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
@@ -1006,7 +996,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>23</v>
@@ -1036,7 +1026,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>61</v>
@@ -1068,7 +1058,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>62</v>
@@ -1098,7 +1088,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>63</v>
@@ -1130,7 +1120,7 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>64</v>
@@ -1161,9 +1151,7 @@
     <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
-      <c r="C21" s="4">
-        <v>15</v>
-      </c>
+      <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
         <v>24</v>
       </c>
@@ -1192,7 +1180,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>25</v>
